--- a/results/qwen3_8b/comparison_GoTRAG/GoTRAG_evaluated.xlsx
+++ b/results/qwen3_8b/comparison_GoTRAG/GoTRAG_evaluated.xlsx
@@ -529,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0.2586206896551724</v>
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L4" t="n">
         <v>0.3181818181818182</v>
@@ -658,7 +658,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0.3037974683544304</v>
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0.2123893805309734</v>
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L9" t="n">
         <v>0.3134328358208955</v>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L10" t="n">
         <v>0.3278688524590164</v>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0.2659574468085106</v>
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0.3389830508474576</v>
@@ -1045,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="n">
         <v>0.3220338983050847</v>
@@ -1131,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L16" t="n">
         <v>0.3163265306122449</v>
@@ -1260,7 +1260,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0.2195121951219512</v>
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
         <v>0.3076923076923077</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0.2666666666666667</v>
@@ -1475,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L24" t="n">
         <v>0.256</v>
@@ -1518,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
         <v>0.3177570093457944</v>
@@ -1604,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0.2891566265060241</v>
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0.2978723404255319</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L30" t="n">
         <v>0.264367816091954</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0.3125</v>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0.3</v>
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
         <v>0.2941176470588235</v>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L35" t="n">
         <v>0.2844036697247707</v>
@@ -1991,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0.3962264150943396</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0.373134328358209</v>
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L42" t="n">
         <v>0.2727272727272727</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L43" t="n">
         <v>0.3023255813953488</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0.2708333333333333</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0.3387096774193548</v>
@@ -2507,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0.3214285714285715</v>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="n">
         <v>0.264367816091954</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0.3392857142857143</v>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0.2567567567567567</v>
@@ -2722,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L53" t="n">
         <v>0.3050847457627119</v>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0.2571428571428571</v>
@@ -2937,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0.3780487804878049</v>
@@ -2980,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0.2702702702702703</v>
@@ -3066,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0.2950819672131147</v>
@@ -3109,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0.2982456140350877</v>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0.25</v>
@@ -3195,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="L64" t="n">
         <v>0.2935779816513762</v>
@@ -3281,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0.2746478873239437</v>
@@ -3367,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0.2335329341317365</v>
